--- a/09-Case and Ticket Management/case-ticket-management-testcases.xlsx
+++ b/09-Case and Ticket Management/case-ticket-management-testcases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="361">
   <si>
     <t>📋  META</t>
   </si>
@@ -170,10 +170,10 @@
     <t>Select a Case Type</t>
   </si>
   <si>
-    <t>Types = "1002-Camera Malfunction -Repair"</t>
-  </si>
-  <si>
-    <t>Priority badge automatically shows "High Priority" (orange) in the top-right of the form</t>
+    <t>Types = "1002-Camera Malfunction -Repair" (Priority value = 3 per Case Configuration matrix)</t>
+  </si>
+  <si>
+    <t>Priority badge automatically shows "High Priority" (Red) — priority 3 falls in the 1–3 range per Q15 mapping confirmed 2026-06-25</t>
   </si>
   <si>
     <t>A Customer Profile "Somying Rakdee" with phone 081-234-5678 exists in the system</t>
@@ -543,6 +543,92 @@
   </si>
   <si>
     <t>File is added to the case and shown in the attachment list</t>
+  </si>
+  <si>
+    <t>TS-05</t>
+  </si>
+  <si>
+    <t>Priority auto-set — verify all 6 distinct priority levels (matrix 2026-06-22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Priority auto-set by Case Type (AC3)
+2. Case Type matrix verified 2026-06-22: 11 device types / 27 sub-types / priority values 3,4,6,7,8,9
+3. Q15 resolved 2026-06-25: 0=Critical(Red) · 1–3=High(Red) · 4–6=Medium(Yellow) · 7–9=Low(Blue)</t>
+  </si>
+  <si>
+    <t>TS-05_TC-01</t>
+  </si>
+  <si>
+    <t>Priority 3 — Camera Malfunction Repair</t>
+  </si>
+  <si>
+    <t>Select the Case Type dropdown and choose the sub-type</t>
+  </si>
+  <si>
+    <t>Types = "1002-Camera Malfunction -Repair" (Priority 3, SLA 97min, Workflow: BMA-Camera Flow)</t>
+  </si>
+  <si>
+    <t>Priority badge appears automatically showing "High Priority" (Red) — priority 3 falls in the 1–3 range</t>
+  </si>
+  <si>
+    <t>TS-05_TC-02</t>
+  </si>
+  <si>
+    <t>Priority 4 — Camera Malfunction Investigation</t>
+  </si>
+  <si>
+    <t>Types = "1001-Camera Malfunction -Investigation" (Priority 4, SLA 97min, Workflow: BMA-Camera Flow)</t>
+  </si>
+  <si>
+    <t>Priority badge shows "Medium Priority" (Yellow) — priority 4 falls in the 4–6 range</t>
+  </si>
+  <si>
+    <t>TS-05_TC-03</t>
+  </si>
+  <si>
+    <t>Priority 6 — Camera Malfunction Service</t>
+  </si>
+  <si>
+    <t>Types = "1003-Camera Malfunction -Service" (Priority 6, SLA 97min, Workflow: BMA-Camera Flow)</t>
+  </si>
+  <si>
+    <t>Priority badge shows "Medium Priority" (Yellow) — priority 6 is the upper boundary of the 4–6 range</t>
+  </si>
+  <si>
+    <t>TS-05_TC-04</t>
+  </si>
+  <si>
+    <t>Priority 7 — Water Monitoring Devices Investigation</t>
+  </si>
+  <si>
+    <t>Types = "2001-Water Monitoring Devices -Investigation" (Priority 7, SLA 100min, Workflow: BMA-Water Monitoring Devices Flow)</t>
+  </si>
+  <si>
+    <t>Priority badge shows "Low Priority" (Blue) — priority 7 falls in the 7–9 range; SLA also changes to 100 min</t>
+  </si>
+  <si>
+    <t>TS-05_TC-05</t>
+  </si>
+  <si>
+    <t>Priority 8 — Water Monitoring Devices Maintenance</t>
+  </si>
+  <si>
+    <t>Types = "2004-Water Monitoring Devices -Maintenance" (Priority 8, SLA 100min, Workflow: BMA-Water Monitoring Devices Flow)</t>
+  </si>
+  <si>
+    <t>Priority badge shows "Low Priority" (Blue) — priority 8 falls in the 7–9 range</t>
+  </si>
+  <si>
+    <t>TS-05_TC-06</t>
+  </si>
+  <si>
+    <t>Priority 9 — Water Monitoring Devices Outsourced</t>
+  </si>
+  <si>
+    <t>Types = "2005-Water Monitoring Devices -Outsourced" (Priority 9, SLA 100min, Workflow: BMA-Water Monitoring Devices Flow)</t>
+  </si>
+  <si>
+    <t>Priority badge shows "Low Priority" (Blue) — priority 9 is the highest value in the current matrix and the upper boundary of the 7–9 range</t>
   </si>
   <si>
     <t>TS-04</t>
@@ -1454,7 +1540,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -2623,7 +2709,7 @@
         <v>173</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>174</v>
@@ -2667,13 +2753,13 @@
         <v>173</v>
       </c>
       <c r="G27" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="I27" s="8" t="s">
         <v>180</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>181</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>39</v>
@@ -2682,13 +2768,13 @@
         <v>40</v>
       </c>
       <c r="L27" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="N27" s="8" t="s">
         <v>182</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2711,13 +2797,13 @@
         <v>173</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>184</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>186</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>39</v>
@@ -2726,13 +2812,13 @@
         <v>40</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2746,37 +2832,37 @@
         <v>32</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>194</v>
+        <v>39</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2790,37 +2876,37 @@
         <v>32</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J30" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="N30" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="N30" s="8" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2834,22 +2920,22 @@
         <v>32</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>39</v>
@@ -2858,13 +2944,13 @@
         <v>40</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2878,22 +2964,22 @@
         <v>32</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>39</v>
@@ -2902,13 +2988,13 @@
         <v>40</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -2922,37 +3008,37 @@
         <v>32</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>194</v>
+        <v>39</v>
       </c>
       <c r="K33" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>220</v>
+        <v>42</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -2966,22 +3052,22 @@
         <v>32</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>44</v>
+        <v>212</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>39</v>
@@ -2990,13 +3076,13 @@
         <v>40</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>228</v>
+        <v>42</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -3010,37 +3096,37 @@
         <v>32</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K35" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -3054,37 +3140,37 @@
         <v>32</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K36" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -3098,22 +3184,22 @@
         <v>32</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>44</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>39</v>
@@ -3122,13 +3208,13 @@
         <v>40</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -3142,22 +3228,22 @@
         <v>32</v>
       </c>
       <c r="D38" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="I38" s="8" t="s">
         <v>240</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>250</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>39</v>
@@ -3166,13 +3252,13 @@
         <v>40</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>71</v>
+        <v>241</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>42</v>
+        <v>242</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -3186,37 +3272,37 @@
         <v>32</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>53</v>
+        <v>247</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -3230,37 +3316,37 @@
         <v>32</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>263</v>
+        <v>44</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>194</v>
+        <v>39</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>42</v>
+        <v>256</v>
       </c>
       <c r="N40" s="8" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -3274,37 +3360,37 @@
         <v>32</v>
       </c>
       <c r="D41" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L41" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="M41" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="N41" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="M41" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N41" s="8" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -3318,37 +3404,37 @@
         <v>32</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>276</v>
+        <v>44</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="N42" s="8" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -3362,37 +3448,37 @@
         <v>32</v>
       </c>
       <c r="D43" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L43" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="M43" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="N43" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -3406,37 +3492,37 @@
         <v>32</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>194</v>
+        <v>39</v>
       </c>
       <c r="K44" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>294</v>
+        <v>71</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>295</v>
+        <v>42</v>
       </c>
       <c r="N44" s="8" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -3450,37 +3536,37 @@
         <v>32</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>39</v>
+        <v>222</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>300</v>
+        <v>53</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -3494,37 +3580,37 @@
         <v>32</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>310</v>
+        <v>42</v>
       </c>
       <c r="N46" s="8" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -3538,37 +3624,37 @@
         <v>32</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K47" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="M47" s="8" t="s">
         <v>42</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -3582,37 +3668,37 @@
         <v>32</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K48" s="8" t="s">
         <v>40</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>42</v>
+        <v>308</v>
       </c>
       <c r="N48" s="8" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -3626,37 +3712,301 @@
         <v>32</v>
       </c>
       <c r="D49" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M49" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="G51" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="H51" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="I51" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="J51" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L51" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="H49" s="8" t="s">
+      <c r="M51" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="N51" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="J49" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L49" s="8" t="s">
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="M49" s="8" t="s">
+      <c r="E52" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="M53" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="N49" s="8" t="s">
-        <v>332</v>
+      <c r="N53" s="8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N54" s="8" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
